--- a/data/gravel/Amigo Bug Out 2025.xlsx
+++ b/data/gravel/Amigo Bug Out 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10905"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{354A142E-28FF-3F44-9E1B-C0FB7054EC05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE3E7606-0F7B-F744-A829-FCADD14FD714}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12400" yWindow="2320" windowWidth="24840" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3960" yWindow="2320" windowWidth="24840" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/data/gravel/Amigo Bug Out 2025.xlsx
+++ b/data/gravel/Amigo Bug Out 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE3E7606-0F7B-F744-A829-FCADD14FD714}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18ECBA8E-7ACB-5F4E-94C0-B468B763E6A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3960" yWindow="2320" windowWidth="24840" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="126">
   <si>
     <t>brand</t>
   </si>
@@ -395,6 +395,9 @@
   </si>
   <si>
     <t>yes</t>
+  </si>
+  <si>
+    <t>https://amigoframeworks.com/cdn/shop/products/AmigoFrameworks_Bugout_pc-MichaelTregelles-4_740x.jpg?v=1689962203</t>
   </si>
 </sst>
 </file>
@@ -780,6 +783,11 @@
         <v>120</v>
       </c>
     </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>125</v>
+      </c>
+    </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>8</v>

--- a/data/gravel/Amigo Bug Out 2025.xlsx
+++ b/data/gravel/Amigo Bug Out 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18ECBA8E-7ACB-5F4E-94C0-B468B763E6A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1066C83A-14AD-5F47-B17C-065D80D3FD88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3960" yWindow="2320" windowWidth="24840" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="128">
   <si>
     <t>brand</t>
   </si>
@@ -398,6 +398,12 @@
   </si>
   <si>
     <t>https://amigoframeworks.com/cdn/shop/products/AmigoFrameworks_Bugout_pc-MichaelTregelles-4_740x.jpg?v=1689962203</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Nashville, TN, USA</t>
   </si>
 </sst>
 </file>
@@ -737,7 +743,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F83"/>
+  <dimension ref="A1:F84"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1720,6 +1726,14 @@
         <v>122</v>
       </c>
     </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>126</v>
+      </c>
+      <c r="B84" t="s">
+        <v>127</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Amigo Bug Out 2025.xlsx
+++ b/data/gravel/Amigo Bug Out 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1066C83A-14AD-5F47-B17C-065D80D3FD88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6825FDEA-1245-674F-8EF6-D97690D668B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3960" yWindow="2320" windowWidth="24840" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="134">
   <si>
     <t>brand</t>
   </si>
@@ -404,6 +404,24 @@
   </si>
   <si>
     <t>Nashville, TN, USA</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -743,7 +761,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F84"/>
+  <dimension ref="A1:F90"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1575,162 +1593,192 @@
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>90</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>91</v>
+        <v>129</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>92</v>
-      </c>
-      <c r="B62">
-        <v>31.6</v>
+        <v>130</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>93</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>94</v>
-      </c>
-      <c r="B64">
-        <v>44</v>
+        <v>132</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>95</v>
-      </c>
-      <c r="B65">
-        <v>46</v>
+        <v>133</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>96</v>
+        <v>90</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>97</v>
-      </c>
-      <c r="B67">
-        <v>160</v>
+        <v>91</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>98</v>
+        <v>92</v>
+      </c>
+      <c r="B68">
+        <v>31.6</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>99</v>
+        <v>93</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>100</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>121</v>
+        <v>94</v>
+      </c>
+      <c r="B70">
+        <v>44</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>101</v>
+        <v>95</v>
+      </c>
+      <c r="B71">
+        <v>46</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="B73">
-        <v>2</v>
+        <v>160</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>104</v>
-      </c>
-      <c r="B74">
-        <v>1</v>
+        <v>98</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>106</v>
+        <v>100</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>109</v>
+        <v>103</v>
+      </c>
+      <c r="B79">
+        <v>2</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="B80">
-        <v>2800</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>113</v>
-      </c>
-      <c r="B83" s="2" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>110</v>
+      </c>
+      <c r="B86">
+        <v>2800</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>113</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
         <v>126</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B90" t="s">
         <v>127</v>
       </c>
     </row>
